--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.29333353249464</v>
+        <v>9.310166699030379</v>
       </c>
       <c r="D2" t="n">
-        <v>57.32155236967083</v>
+        <v>9.31475226007151</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F2" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.13733397881881</v>
+        <v>6.522316771558057</v>
       </c>
       <c r="D3" t="n">
-        <v>40.01001095798095</v>
+        <v>6.501626780671905</v>
       </c>
       <c r="E3" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F3" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.6589754584455</v>
+        <v>6.607083511997393</v>
       </c>
       <c r="D4" t="n">
-        <v>40.47051759288328</v>
+        <v>6.576459108843532</v>
       </c>
       <c r="E4" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F4" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.18562897272178</v>
+        <v>5.23016470806729</v>
       </c>
       <c r="D5" t="n">
-        <v>32.32861858403573</v>
+        <v>5.253400519905806</v>
       </c>
       <c r="E5" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F5" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.50513346731356</v>
+        <v>6.419584188438455</v>
       </c>
       <c r="D6" t="n">
-        <v>39.31033401356794</v>
+        <v>6.38792927720479</v>
       </c>
       <c r="E6" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F6" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.59288781442942</v>
+        <v>6.27134426984478</v>
       </c>
       <c r="D7" t="n">
-        <v>38.76314046814073</v>
+        <v>6.299010326072868</v>
       </c>
       <c r="E7" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F7" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7.860708329683499</v>
+        <v>1.277365103573569</v>
       </c>
       <c r="D8" t="n">
-        <v>7.665557210863671</v>
+        <v>1.245653046765347</v>
       </c>
       <c r="E8" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F8" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.43648380719706</v>
+        <v>6.245928618669522</v>
       </c>
       <c r="D9" t="n">
-        <v>38.62839052309742</v>
+        <v>6.277113460003331</v>
       </c>
       <c r="E9" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F9" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.28334160357532</v>
+        <v>3.133543010580989</v>
       </c>
       <c r="D10" t="n">
-        <v>19.13071568451688</v>
+        <v>3.108741298733994</v>
       </c>
       <c r="E10" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F10" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.1881821469951</v>
+        <v>5.230579598886703</v>
       </c>
       <c r="D11" t="n">
-        <v>32.38073973226638</v>
+        <v>5.261870206493287</v>
       </c>
       <c r="E11" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F11" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.96006637499291</v>
+        <v>5.193510785936349</v>
       </c>
       <c r="D12" t="n">
-        <v>19.51587190819833</v>
+        <v>3.17132918508223</v>
       </c>
       <c r="E12" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F12" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.53545451084676</v>
+        <v>6.262011358012599</v>
       </c>
       <c r="D13" t="n">
-        <v>19.00657780874821</v>
+        <v>3.088568893921584</v>
       </c>
       <c r="E13" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F13" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>36.89570836009217</v>
+        <v>5.995552608514978</v>
       </c>
       <c r="D14" t="n">
-        <v>37.07611227299527</v>
+        <v>6.024868244361732</v>
       </c>
       <c r="E14" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F14" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>45.30194595033434</v>
+        <v>7.361566216929331</v>
       </c>
       <c r="D15" t="n">
-        <v>45.45095519437061</v>
+        <v>7.385780219085224</v>
       </c>
       <c r="E15" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F15" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>48.23258748157711</v>
+        <v>7.837795465756281</v>
       </c>
       <c r="D16" t="n">
-        <v>29.55007873477943</v>
+        <v>4.801887794401658</v>
       </c>
       <c r="E16" t="n">
-        <v>11.1770746303027</v>
+        <v>1.816274627424189</v>
       </c>
       <c r="F16" t="n">
-        <v>12.1029826459567</v>
+        <v>1.966734679967963</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
